--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,11 +88,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -107,13 +175,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -122,7 +190,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -137,13 +205,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,79 +88,11 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -175,13 +107,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -190,7 +122,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -205,13 +137,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -19021,7 +18953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19159,6 +19091,38 @@
         <v>119</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Hojas extraídas</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Celdas con valor extraídas</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2980320</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Archivo valores CSV.GZ</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>assets/data/ine/csv/ove_ine_venezuela_celdas_tabulares.csv.gz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,84 +85,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -175,13 +112,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -190,7 +130,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -205,13 +145,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -19135,7 +19078,7 @@
           <t>Número de recursos</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7" t="n">
         <v>323</v>
       </c>
     </row>
@@ -19145,7 +19088,7 @@
           <t>Recursos tabulares</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="7" t="n">
         <v>204</v>
       </c>
     </row>
@@ -19155,7 +19098,7 @@
           <t>Documentos</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="7" t="n">
         <v>119</v>
       </c>
     </row>
@@ -19165,7 +19108,7 @@
           <t>Hojas extraídas</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="7" t="n">
         <v>220</v>
       </c>
     </row>
@@ -19175,7 +19118,7 @@
           <t>Celdas con valor extraídas</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="7" t="n">
         <v>2980320</v>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,11 +93,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -112,16 +180,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -130,7 +195,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -145,16 +210,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -19094,7 +19094,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K329"/>
+  <dimension ref="A1:K332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Noticias-Julio-29-07-2026.pdf</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -17342,17 +17342,17 @@
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>Noticias-Julio-29-07-2026.pdf</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Noticias-Julio-29-07-2026.pdf</t>
         </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17394,22 +17394,22 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17451,22 +17451,22 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17508,22 +17508,22 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17565,22 +17565,22 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17632,12 +17632,12 @@
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17679,22 +17679,22 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17741,17 +17741,17 @@
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17798,17 +17798,17 @@
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17850,22 +17850,22 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17907,22 +17907,22 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17969,17 +17969,17 @@
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18021,22 +18021,22 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18083,17 +18083,17 @@
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18135,22 +18135,22 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18192,22 +18192,22 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18249,22 +18249,22 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18368,17 +18368,17 @@
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18430,12 +18430,12 @@
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,12 +18571,12 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -18653,17 +18653,17 @@
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>Censo_de_estructuras_viviendas_y_personas_en_las_zonas_afectadas.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Censo_de_estructuras_viviendas_y_personas_en_las_zonas_afectadas.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
@@ -18772,12 +18772,12 @@
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Encuesta Hogares 1967-1997</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18809,12 +18809,12 @@
       </c>
       <c r="E326" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18866,32 +18866,32 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18923,12 +18923,12 @@
       </c>
       <c r="E328" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -18938,17 +18938,17 @@
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -19000,15 +19000,186 @@
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
+          <t>Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J329" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K329" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E330" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H330" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I330" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="K330" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H331" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J331" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H332" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr">
+        <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J329" s="4" t="inlineStr">
+      <c r="J332" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K329" s="4" t="inlineStr">
+      <c r="K332" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19094,7 +19265,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19312,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14">
@@ -19161,7 +19332,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K332"/>
+  <dimension ref="A1:K333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -16487,17 +16487,17 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JUNIO_2025.pdf</t>
+          <t>Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="K285" s="4" t="inlineStr">
@@ -16544,17 +16544,17 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr">
         <is>
-          <t>Noticias-12-06-al-19-06.pdf</t>
+          <t>Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -16596,22 +16596,22 @@
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LA-GUAIRA.pdf</t>
+          <t>Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="K287" s="4" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -16663,12 +16663,12 @@
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LARA.pdf</t>
+          <t>ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="K288" s="4" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Las escala subregional y local en la planificación</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Las escala subregional y local en la planificación</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -16767,22 +16767,22 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>MANUAL.pdf</t>
+          <t>E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Mapa Pobreza XII Censo</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -16824,22 +16824,22 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>MANUAL.pdf</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
         </is>
       </c>
       <c r="K291" s="4" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Mapa Pobreza XII Censo</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -16886,17 +16886,17 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2025.pdf</t>
+          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="K292" s="4" t="inlineStr">
@@ -16943,17 +16943,17 @@
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2026.pdf</t>
+          <t>Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="K293" s="4" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2025.pdf</t>
+          <t>Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="K294" s="4" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2026-1.pdf</t>
+          <t>Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -17109,22 +17109,22 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MIRANDA.pdf</t>
+          <t>Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="K296" s="4" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -17176,12 +17176,12 @@
       </c>
       <c r="I297" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MONAGAS.pdf</t>
+          <t>ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="K297" s="4" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -17233,12 +17233,12 @@
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MERIDA.pdf</t>
+          <t>ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -17285,17 +17285,17 @@
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Julio-29-07-2026.pdf</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -17347,12 +17347,12 @@
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Julio-29-07-2026.pdf</t>
+          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Noticias-Julio-29-07-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Noticias-Agosto-05-08-2026.pdf</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17399,17 +17399,17 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>Noticias-Agosto-05-08-2026.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-05-08-2026.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17451,22 +17451,22 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17508,22 +17508,22 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17565,22 +17565,22 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17622,22 +17622,22 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17689,12 +17689,12 @@
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17736,22 +17736,22 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17798,17 +17798,17 @@
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17907,22 +17907,22 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17964,22 +17964,22 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18026,17 +18026,17 @@
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18078,22 +18078,22 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18140,17 +18140,17 @@
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18192,22 +18192,22 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18249,22 +18249,22 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18368,17 +18368,17 @@
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18420,22 +18420,22 @@
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18648,22 +18648,22 @@
       </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,12 +18685,12 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18824,17 +18824,17 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Encuesta Hogares 1967-1997</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18876,22 +18876,22 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
@@ -18943,12 +18943,12 @@
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18980,12 +18980,12 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -18995,17 +18995,17 @@
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19057,12 +19057,12 @@
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>Aragua.xls</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19171,15 +19171,72 @@
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J332" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K332" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H333" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J332" s="4" t="inlineStr">
+      <c r="J333" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K332" s="4" t="inlineStr">
+      <c r="K333" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19265,7 +19322,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19369,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -19332,7 +19389,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K333"/>
+  <dimension ref="A1:K334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto-05-08-2026.pdf</t>
+          <t>Noticias-Agosto1.pdf</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17404,12 +17404,12 @@
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto-05-08-2026.pdf</t>
+          <t>Noticias-Agosto1.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-05-08-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto1.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Noticias-Agosto2.pdf</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17456,17 +17456,17 @@
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>Noticias-Agosto2.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto2.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17508,22 +17508,22 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17565,22 +17565,22 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17622,22 +17622,22 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17679,22 +17679,22 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17746,12 +17746,12 @@
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17793,22 +17793,22 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17912,17 +17912,17 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17964,22 +17964,22 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18021,22 +18021,22 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18083,17 +18083,17 @@
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18135,22 +18135,22 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18197,17 +18197,17 @@
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18249,22 +18249,22 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18425,17 +18425,17 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18591,22 +18591,22 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18658,12 +18658,12 @@
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,12 +18742,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18819,22 +18819,22 @@
       </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18881,17 +18881,17 @@
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Encuesta Hogares 1967-1997</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18933,22 +18933,22 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -19000,12 +19000,12 @@
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -19052,17 +19052,17 @@
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>Aragua.xls</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19171,12 +19171,12 @@
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="K332" s="4" t="inlineStr">
@@ -19228,15 +19228,72 @@
       </c>
       <c r="I333" s="4" t="inlineStr">
         <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E334" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H334" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I334" s="4" t="inlineStr">
+        <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J333" s="4" t="inlineStr">
+      <c r="J334" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K333" s="4" t="inlineStr">
+      <c r="K334" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19322,7 +19379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -19369,7 +19426,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14">
@@ -19389,7 +19446,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K334"/>
+  <dimension ref="A1:K333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto1.pdf</t>
+          <t>Noticias-Agosto5.pdf</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17404,12 +17404,12 @@
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto1.pdf</t>
+          <t>Noticias-Agosto5.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto5.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto2.pdf</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17456,17 +17456,17 @@
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto2.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto2.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17508,22 +17508,22 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17565,22 +17565,22 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17622,22 +17622,22 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17679,22 +17679,22 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17746,12 +17746,12 @@
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17793,22 +17793,22 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17912,17 +17912,17 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17964,22 +17964,22 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18021,22 +18021,22 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18083,17 +18083,17 @@
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18135,22 +18135,22 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18197,17 +18197,17 @@
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18249,22 +18249,22 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18425,17 +18425,17 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18591,22 +18591,22 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18658,12 +18658,12 @@
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,12 +18742,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Vivienda y servicios</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Censo de zonas afectadas del estado Vargas</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -18819,22 +18819,22 @@
       </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Encuesta Hogares 1967-1997</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -18881,17 +18881,17 @@
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Estado Aragua</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -18933,22 +18933,22 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
@@ -19000,12 +19000,12 @@
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Aragua</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
@@ -19052,17 +19052,17 @@
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>Aragua.xls</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19171,12 +19171,12 @@
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>Estado-Aragua.xls</t>
         </is>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
         </is>
       </c>
       <c r="K332" s="4" t="inlineStr">
@@ -19228,72 +19228,15 @@
       </c>
       <c r="I333" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
       <c r="K333" s="4" t="inlineStr">
-        <is>
-          <t>https://ine.gob.ve/</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="4" t="inlineStr">
-        <is>
-          <t>INE Venezuela - Instituto Nacional de Estadística</t>
-        </is>
-      </c>
-      <c r="B334" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C334" s="4" t="inlineStr">
-        <is>
-          <t>Aragua</t>
-        </is>
-      </c>
-      <c r="D334" s="4" t="inlineStr">
-        <is>
-          <t>Vivienda y servicios</t>
-        </is>
-      </c>
-      <c r="E334" s="4" t="inlineStr">
-        <is>
-          <t>Dato tabular</t>
-        </is>
-      </c>
-      <c r="F334" s="4" t="inlineStr">
-        <is>
-          <t>XLS</t>
-        </is>
-      </c>
-      <c r="G334" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H334" s="4" t="inlineStr">
-        <is>
-          <t>abril</t>
-        </is>
-      </c>
-      <c r="I334" s="4" t="inlineStr">
-        <is>
-          <t>Estado_Aragua-3.xls</t>
-        </is>
-      </c>
-      <c r="J334" s="4" t="inlineStr">
-        <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
-        </is>
-      </c>
-      <c r="K334" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19379,7 +19322,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19369,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -19446,7 +19389,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_catalogo_recursos.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K333"/>
+  <dimension ref="A1:K340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Anuario Estadístico 2003</t>
+          <t>Anuario Estadístico 1945</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-2003.pdf</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1945.pdf</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/05/ANUARIO-ESTADISTICO-DE-VENEZUELA-2003.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ANUARIO-ESTADISTICO-DE-VENEZUELA-1945.pdf</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Anuarios Estadísticos 1940</t>
+          <t>Anuario Estadístico 1946</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1154,17 +1154,17 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1940.pdf</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1946.pdf</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/05/ANUARIO-ESTADISTICO-DE-VENEZUELA-1940.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ANUARIO-ESTADISTICO-DE-VENEZUELA-1946.pdf</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Amazonas 2001-2011</t>
+          <t>Anuario Estadístico 1947</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Censo 2001-2011</t>
+          <t>Anuarios</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Estado-Amazonas-Censo-2001-y-2011-1.xls</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1947.pdf</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ANUARIO-ESTADISTICO-DE-VENEZUELA-1947.pdf</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1243,22 +1243,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Amazonas 2001-2011</t>
+          <t>Anuario Estadístico 1948</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Censo 2001-2011</t>
+          <t>Anuarios</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Estado-Amazonas-Censo-2001-y-2011.xls</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1948.pdf</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ANUARIO-ESTADISTICO-DE-VENEZUELA-1948.pdf</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1300,22 +1300,22 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui 2001-2011</t>
+          <t>Anuario Estadístico 1949</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Censo 2001-2011</t>
+          <t>Anuarios</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Estado-Anzoategui-Censo-2001-y-2011-1.xls</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1949.pdf</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ANUARIO-ESTADISTICO-DE-VENEZUELA-1949.pdf</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1357,22 +1357,22 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui 2001-2011</t>
+          <t>Anuario Estadístico 2002</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Censo 2001-2011</t>
+          <t>Anuarios</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1382,17 +1382,17 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Estado-Anzoategui-Censo-2001-y-2011.xls</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-2002.pdf</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/ANUARIO-ESTADISTICO-DE-VENEZUELA-2002.pdf</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Apure 2001-2011</t>
+          <t>Anuario Estadístico 2003</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Censo 2001-2011</t>
+          <t>Anuarios</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Estado-Apure-Censo-2001-y-2011-1.xls</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-2003.pdf</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/05/ANUARIO-ESTADISTICO-DE-VENEZUELA-2003.pdf</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1471,22 +1471,22 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Apure 2001-2011</t>
+          <t>Anuarios Estadísticos 1940</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Censo 2001-2011</t>
+          <t>Anuarios</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Estado-Apure-Censo-2001-y-2011.xls</t>
+          <t>ANUARIO-ESTADISTICO-DE-VENEZUELA-1940.pdf</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/05/ANUARIO-ESTADISTICO-DE-VENEZUELA-1940.pdf</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Aragua 2001-2011</t>
+          <t>Amazonas 2001-2011</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-Censo-2001-y-2011.xls</t>
+          <t>Estado-Amazonas-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Barinas 2001-2011</t>
+          <t>Amazonas 2001-2011</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Estado-Barinas-Censo-2001-y-2011.xls</t>
+          <t>Estado-Amazonas-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Bolívar 2001-2011</t>
+          <t>Anzoátegui 2001-2011</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Estado-Bolivar-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Anzoategui-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Bolívar 2001-2011</t>
+          <t>Anzoátegui 2001-2011</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Estado-Bolivar-Censo-2001-y-2011.xls</t>
+          <t>Estado-Anzoategui-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Carabobo 2001-2011</t>
+          <t>Apure 2001-2011</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Estado-Carabobo-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Apure-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Carabobo 2001-2011</t>
+          <t>Apure 2001-2011</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Estado-Carabobo-Censo-2001-y-2011.xls</t>
+          <t>Estado-Apure-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Cojedes 2001-2011</t>
+          <t>Aragua 2001-2011</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Aragua-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Cojedes 2001-2011</t>
+          <t>Barinas 2001-2011</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes-Censo-2001-y-2011.xls</t>
+          <t>Estado-Barinas-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro 2001-2011</t>
+          <t>Bolívar 2001-2011</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Estado-Delta-Amacuro-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Bolivar-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro 2001-2011</t>
+          <t>Bolívar 2001-2011</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Estado-Delta-Amacuro-Censo-2001-y-2011.xls</t>
+          <t>Estado-Bolivar-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Dep. Federales</t>
+          <t>Carabobo 2001-2011</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Dependencias-Federales-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Carabobo-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Dep. Federales 2001-2011</t>
+          <t>Carabobo 2001-2011</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Dependencias-Federales-Censo-2001-y-2011.xls</t>
+          <t>Estado-Carabobo-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Distr. Capital 2001-2011</t>
+          <t>Cojedes 2001-2011</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Cojedes-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Distr. Capital 2001-2011</t>
+          <t>Cojedes 2001-2011</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital-Censo-2001-y-2011.xls</t>
+          <t>Estado-Cojedes-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Falcón 2001-2011</t>
+          <t>Delta Amacuro 2001-2011</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Estado-Falcon-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Delta-Amacuro-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Falcón 2001-2011</t>
+          <t>Delta Amacuro 2001-2011</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Estado-Falcon-Censo-2001-y-2011.xls</t>
+          <t>Estado-Delta-Amacuro-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Guárico 2001-2011</t>
+          <t>Dep. Federales</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico-Censo-2001-y-2011-1.xls</t>
+          <t>Dependencias-Federales-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Guárico 2001-2011</t>
+          <t>Dep. Federales 2001-2011</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico-Censo-2001-y-2011.xls</t>
+          <t>Dependencias-Federales-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>La Guaira 2001-2011</t>
+          <t>Distr. Capital 2001-2011</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira-Censo-2001-y-2011-1.xls</t>
+          <t>Distrito-Capital-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>La Guaira 2001-2011</t>
+          <t>Distr. Capital 2001-2011</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira-Censo-2001-y-2011.xls</t>
+          <t>Distrito-Capital-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Lara 2001-2011</t>
+          <t>Falcón 2001-2011</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Estado-Lara-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Falcon-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Lara 2001-2011</t>
+          <t>Falcón 2001-2011</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Estado-Lara-Censo-2001-y-2011.xls</t>
+          <t>Estado-Falcon-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Miranda 2001-2011</t>
+          <t>Guárico 2001-2011</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Estado-Miranda-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Guarico-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Miranda 2001-2011</t>
+          <t>Guárico 2001-2011</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Estado-Miranda-Censo-2001-y-2011.xls</t>
+          <t>Estado-Guarico-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Monagas 2001-2011</t>
+          <t>La Guaira 2001-2011</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Estado-Monagas-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-La-Guaira-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Monagas 2001-2011</t>
+          <t>La Guaira 2001-2011</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Estado-Monagas-Censo-2001-y-2011.xls</t>
+          <t>Estado-La-Guaira-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Mérida 2001-2011</t>
+          <t>Lara 2001-2011</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Estado-Merida-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Lara-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Mérida 2001-2011</t>
+          <t>Lara 2001-2011</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Estado-Merida-Censo-2001-y-2011.xls</t>
+          <t>Estado-Lara-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Nacional 2001-2011</t>
+          <t>Miranda 2001-2011</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Nacional-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Miranda-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Nacional 2001-2011</t>
+          <t>Miranda 2001-2011</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Nacional-Censo-2001-y-2011.xls</t>
+          <t>Estado-Miranda-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta 2001-2011</t>
+          <t>Monagas 2001-2011</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
+          <t>Estado-Monagas-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta 2001-2011</t>
+          <t>Monagas 2001-2011</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
+          <t>Estado-Monagas-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa 2001-2011</t>
+          <t>Mérida 2001-2011</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Estado-Portuguesa-Censo-2001-y-2011.xls</t>
+          <t>Estado-Merida-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa 2001-2011</t>
+          <t>Mérida 2001-2011</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Estado-Portuguesa.-Censo-2001-y-2011.xls</t>
+          <t>Estado-Merida-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Sucre 2001-2011</t>
+          <t>Nacional 2001-2011</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Estado-Sucre-Censo-2001-y-2011-1.xls</t>
+          <t>Nacional-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Sucre 2001-2011</t>
+          <t>Nacional 2001-2011</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Estado-Sucre-Censo-2001-y-2011.xls</t>
+          <t>Nacional-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Trujillo 2001-2011</t>
+          <t>Nueva Esparta 2001-2011</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Trujillo 2001-2011</t>
+          <t>Nueva Esparta 2001-2011</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo-Censo-2001-y-2011.xls</t>
+          <t>estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/estado-Nueva-Esparta-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Táchira 2001-2011</t>
+          <t>Portuguesa 2001-2011</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Estado-Tachira-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Portuguesa-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Táchira 2001-2011</t>
+          <t>Portuguesa 2001-2011</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Estado-Tachira-Censo-2001-y-2011.xls</t>
+          <t>Estado-Portuguesa.-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy 2001-2011</t>
+          <t>Sucre 2001-2011</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy-Censo-2001-y-2011.xls</t>
+          <t>Estado-Sucre-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy 2001-2011</t>
+          <t>Sucre 2001-2011</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>estado-Yaracuy-Censo-2001-y-2011.xls</t>
+          <t>Estado-Sucre-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/estado-Yaracuy-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Zulia 2001-2011</t>
+          <t>Trujillo 2001-2011</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Estado-Zulia-Censo-2001-y-2011-1.xls</t>
+          <t>Estado-Trujillo-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-Censo-2001-y-2011-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Zulia 2001-2011</t>
+          <t>Trujillo 2001-2011</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Estado-Zulia-Censo-2001-y-2011.xls</t>
+          <t>Estado-Trujillo-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-Censo-2001-y-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -4036,42 +4036,42 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Municipios Censo 2011</t>
+          <t>Táchira 2001-2011</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Censo 2011</t>
+          <t>Censo 2001-2011</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>POBLACION-POR-MUNICIPIOS-CENSO-2011.pdf</t>
+          <t>Estado-Tachira-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/09/POBLACION-POR-MUNICIPIOS-CENSO-2011.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -4093,42 +4093,42 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Parroquias Censo 2011</t>
+          <t>Táchira 2001-2011</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Censo 2011</t>
+          <t>Censo 2001-2011</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>P.-Censo-2011.pdf</t>
+          <t>Estado-Tachira-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/10/P.-Censo-2011.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -4150,42 +4150,42 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Población Indigena Censo 2011</t>
+          <t>Yaracuy 2001-2011</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Censo 2011</t>
+          <t>Censo 2001-2011</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>POBLACION-INDIGENA-CENSO-2011.pdf</t>
+          <t>Estado-Yaracuy-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/09/POBLACION-INDIGENA-CENSO-2011.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -4207,42 +4207,42 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Resumen Censo 2011</t>
+          <t>Yaracuy 2001-2011</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Censo 2011</t>
+          <t>Censo 2001-2011</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>CCENSO-2011-RESULTADOS-BASICOS.pdf</t>
+          <t>estado-Yaracuy-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/09/CCENSO-2011-RESULTADOS-BASICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/estado-Yaracuy-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Agua 2011</t>
+          <t>Zulia 2001-2011</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Censo 2011</t>
+          <t>Censo 2001-2011</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Servicio-Agua-Censo-2011.xls</t>
+          <t>Estado-Zulia-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Agua-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-Censo-2001-y-2011-1.xls</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Alfabetismo</t>
+          <t>Zulia 2001-2011</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Censo 2011</t>
+          <t>Censo 2001-2011</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Alfabetismo-Censo-2011.xls</t>
+          <t>Estado-Zulia-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Alfabetismo-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-Censo-2001-y-2011.xls</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Basura 2011</t>
+          <t>Municipios Censo 2011</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Servicio-Basura-Censo-2011.xls</t>
+          <t>POBLACION-POR-MUNICIPIOS-CENSO-2011.pdf</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Basura-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/09/POBLACION-POR-MUNICIPIOS-CENSO-2011.pdf</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Edad Escolar 2011</t>
+          <t>Parroquias Censo 2011</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -4445,32 +4445,32 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Edad-Escolar-Censo-2011.xls</t>
+          <t>P.-Censo-2011.pdf</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Edad-Escolar-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/10/P.-Censo-2011.pdf</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Eliminación de Excretas 2011</t>
+          <t>Población Indigena Censo 2011</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -4502,32 +4502,32 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Eliminacion-de-Excretas-Censo-2011.xls</t>
+          <t>POBLACION-INDIGENA-CENSO-2011.pdf</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Eliminacion-de-Excretas-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/09/POBLACION-INDIGENA-CENSO-2011.pdf</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Eléctrico 2011</t>
+          <t>Resumen Censo 2011</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -4559,32 +4559,32 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Servicio-Electrico-Censo-2011.xls</t>
+          <t>CCENSO-2011-RESULTADOS-BASICOS.pdf</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Electrico-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/09/CCENSO-2011-RESULTADOS-BASICOS.pdf</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Frecuencia Agua 2011</t>
+          <t>Agua 2011</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Frecuencia-Servicio-Agua-Censo-2011.xls</t>
+          <t>Servicio-Agua-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Frecuencia-Servicio-Agua-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Agua-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Frecuencia Basura</t>
+          <t>Alfabetismo</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Frecuencia-Servicio-Basura-Censo-2011.xls</t>
+          <t>Alfabetismo-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Frecuencia-Servicio-Basura-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Alfabetismo-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Gas Directo 2011</t>
+          <t>Basura 2011</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Servicio-Gas-Directo-Censo-2011.xls</t>
+          <t>Servicio-Basura-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Gas-Directo-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Basura-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Grupos de Edad 2011</t>
+          <t>Edad Escolar 2011</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Grupos-de-Edad-Censo-2011.xls</t>
+          <t>Edad-Escolar-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grupos-de-Edad-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Edad-Escolar-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Por Sexo 2011</t>
+          <t>Eliminación de Excretas 2011</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Por-Sexo-Censo-2011.xls</t>
+          <t>Eliminacion-de-Excretas-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Por-Sexo-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Eliminacion-de-Excretas-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Pueblos Indígenas 2011</t>
+          <t>Eléctrico 2011</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Pueblos-Indigenas-Censo-2011.xls</t>
+          <t>Servicio-Electrico-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Pueblos-Indigenas-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Electrico-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Situación Conyugal 2011</t>
+          <t>Frecuencia Agua 2011</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Situacion-Conyugal-Censo-2011.xls</t>
+          <t>Frecuencia-Servicio-Agua-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Situacion-Conyugal-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Frecuencia-Servicio-Agua-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Urbana/Rural 2011</t>
+          <t>Frecuencia Basura</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Urbana-y-Rural-Censo-2011.xls</t>
+          <t>Frecuencia-Servicio-Basura-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Urbana-y-Rural-Censo-2011.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Frecuencia-Servicio-Basura-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Auditiva</t>
+          <t>Gas Directo 2011</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Auditiva-Censo-2011.xlsx</t>
+          <t>Servicio-Gas-Directo-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Auditiva-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicio-Gas-Directo-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -5119,14 +5119,14 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
+          <t>Grupos de Edad 2011</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
           <t>Censo 2011</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>Censo 2011</t>
-        </is>
-      </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Dato tabular</t>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>Servicios-Censo_2011.xlsx</t>
+          <t>Grupos-de-Edad-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicios-Censo_2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grupos-de-Edad-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Condición Vivienda 2011</t>
+          <t>Por Sexo 2011</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>Condicion-Vivienda-Censo-2011.xlsx</t>
+          <t>Por-Sexo-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Condicion-Vivienda-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Por-Sexo-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Deficiencia Económica</t>
+          <t>Pueblos Indígenas 2011</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Deficiencia-Economica-Censo-2011.xlsx</t>
+          <t>Pueblos-Indigenas-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Deficiencia-Economica-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Pueblos-Indigenas-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Grupos de Edad 2011</t>
+          <t>Situación Conyugal 2011</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>Poblacion-Grupos-Edad-Censo-2011-1.xlsx</t>
+          <t>Situacion-Conyugal-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Grupos-Edad-Censo-2011-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Situacion-Conyugal-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Grupos de Edad 2011</t>
+          <t>Urbana/Rural 2011</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>Poblacion-Grupos-Edad-Censo-2011.xlsx</t>
+          <t>Urbana-y-Rural-Censo-2011.xls</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Grupos-Edad-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Urbana-y-Rural-Censo-2011.xls</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Hacinamiento 2011</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>Hacinamiento-Censo-2011.xlsx</t>
+          <t>Discapacidad-Auditiva-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Hacinamiento-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Auditiva-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Lugar de Nacimiento 2011</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>Lugar-Nacimiento-Censo-2011-1.xlsx</t>
+          <t>Servicios-Censo_2011.xlsx</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lugar-Nacimiento-Censo-2011-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Servicios-Censo_2011.xlsx</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Lugar de Nacimiento 2011</t>
+          <t>Condición Vivienda 2011</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>Lugar-Nacimiento-Censo-2011.xlsx</t>
+          <t>Condicion-Vivienda-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lugar-Nacimiento-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Condicion-Vivienda-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Mental/Cardiovascular</t>
+          <t>Deficiencia Económica</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Cardiovascular-Censo-2011.xlsx</t>
+          <t>Deficiencia-Economica-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Cardiovascular-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Deficiencia-Economica-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Mental/Intelectual</t>
+          <t>Grupos de Edad 2011</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Mental-Intelectual-Censo-2011.xlsx</t>
+          <t>Poblacion-Grupos-Edad-Censo-2011-1.xlsx</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Mental-Intelectual-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Grupos-Edad-Censo-2011-1.xlsx</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Mental/Psicosocial</t>
+          <t>Grupos de Edad 2011</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Mental-Psicosocial-Censo-2011.xlsx</t>
+          <t>Poblacion-Grupos-Edad-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Mental-Psicosocial-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Grupos-Edad-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Musculo/Esquelética</t>
+          <t>Hacinamiento 2011</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Musculo-Esquelatica-Censo-2011.xlsx</t>
+          <t>Hacinamiento-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Musculo-Esquelatica-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Hacinamiento-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Nacido en Venezuela 2011</t>
+          <t>Lugar de Nacimiento 2011</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Poblacion-Nacida-Venezuela-Censo-2011.xlsx</t>
+          <t>Lugar-Nacimiento-Censo-2011-1.xlsx</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Nacida-Venezuela-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lugar-Nacimiento-Censo-2011-1.xlsx</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Nacidos en Venezuela 2011</t>
+          <t>Lugar de Nacimiento 2011</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Poblacion-Nacida-en-Venezuela-Censo-2011.xlsx</t>
+          <t>Lugar-Nacimiento-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Nacida-en-Venezuela-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lugar-Nacimiento-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Neurológica</t>
+          <t>Mental/Cardiovascular</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Neurologica-Censo-2011.xlsx</t>
+          <t>Discapacidad-Cardiovascular-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Neurologica-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Cardiovascular-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Población por Sexo 2011</t>
+          <t>Mental/Intelectual</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Poblacion-Sexo-Censo-2011-1.xlsx</t>
+          <t>Discapacidad-Mental-Intelectual-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Sexo-Censo-2011-1.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Mental-Intelectual-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Por Sexo 2011</t>
+          <t>Mental/Psicosocial</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Poblacion-Sexo-Censo-2011.xlsx</t>
+          <t>Discapacidad-Mental-Psicosocial-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Sexo-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Mental-Psicosocial-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Respiratoria</t>
+          <t>Musculo/Esquelética</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Respitaroria-Censo-2011.xlsx</t>
+          <t>Discapacidad-Musculo-Esquelatica-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Respitaroria-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Musculo-Esquelatica-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Nacido en Venezuela 2011</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Visual-Censo-2011.xlsx</t>
+          <t>Poblacion-Nacida-Venezuela-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Visual-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Nacida-Venezuela-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Viviendas Ocupadas 2011</t>
+          <t>Nacidos en Venezuela 2011</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Viviendas-Ocupadas-Censo-2011.xlsx</t>
+          <t>Poblacion-Nacida-en-Venezuela-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Viviendas-Ocupadas-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Nacida-en-Venezuela-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Viviendas, Hogares y Personas</t>
+          <t>Neurológica</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6284,17 +6284,17 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDAS-HOGARES-Y-PERSONAS-CENSO-2011.xlsx</t>
+          <t>Discapacidad-Neurologica-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/VIVIENDAS-HOGARES-Y-PERSONAS-CENSO-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Neurologica-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Voz/Habla</t>
+          <t>Población por Sexo 2011</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad-Voz-Habla-Censo-2011.xlsx</t>
+          <t>Poblacion-Sexo-Censo-2011-1.xlsx</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Voz-Habla-Censo-2011.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Sexo-Censo-2011-1.xlsx</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Por Capítulo 1998-2018</t>
+          <t>Por Sexo 2011</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Comercio exterior</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Exportaciones-po-Capitulo-1998-2018.xls</t>
+          <t>Poblacion-Sexo-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Exportaciones-po-Capitulo-1998-2018.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Poblacion-Sexo-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Por Capítulo 1998-2018</t>
+          <t>Respiratoria</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Comercio exterior</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Importaciones-por-Capitulo-1998-2018.xls</t>
+          <t>Discapacidad-Respitaroria-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Importaciones-por-Capitulo-1998-2018.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Respitaroria-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Tabulados Básicos</t>
+          <t>Visual</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Encuesta de hogares</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>TRABAJO-2001-2023.xls</t>
+          <t>Discapacidad-Visual-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/TRABAJO-2001-2023.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Visual-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Por Tipo</t>
+          <t>Viviendas Ocupadas 2011</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Encuesta de hogares</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>POR-TIPO-1998-2023.xlsx</t>
+          <t>Viviendas-Ocupadas-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-TIPO-1998-2023.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Viviendas-Ocupadas-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Por Variable</t>
+          <t>Viviendas, Hogares y Personas</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Encuesta de hogares</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>POR-VARIABLE-1998-2023.xlsx</t>
+          <t>VIVIENDAS-HOGARES-Y-PERSONAS-CENSO-2011.xlsx</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-VARIABLE-1998-2023.xlsx</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/VIVIENDAS-HOGARES-Y-PERSONAS-CENSO-2011.xlsx</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Divorcios</t>
+          <t>Voz/Habla</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Censo 2011</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>DIVORCIOS.xls</t>
+          <t>Discapacidad-Voz-Habla-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/DIVORCIOS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Discapacidad-Voz-Habla-Censo-2011.xlsx</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Por Entidad</t>
+          <t>Por Capítulo 1998-2018</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Comercio exterior</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>POR-ENTIDAD-Defunciones.xls</t>
+          <t>Exportaciones-po-Capitulo-1998-2018.xls</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Defunciones.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Exportaciones-po-Capitulo-1998-2018.xls</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Por Entidad</t>
+          <t>Por Capítulo 1998-2018</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Comercio exterior</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>POR-ENTIDAD-Matrimonios.xls</t>
+          <t>Importaciones-por-Capitulo-1998-2018.xls</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Matrimonios.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Importaciones-por-Capitulo-1998-2018.xls</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Por Entidad</t>
+          <t>Tabulados Básicos</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Encuesta de hogares</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>POR-ENTIDAD-nacimientos.xls</t>
+          <t>TRABAJO-2001-2023.xls</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-nacimientos.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/TRABAJO-2001-2023.xls</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Por Municipios</t>
+          <t>Por Tipo</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Encuesta de hogares</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>POR-MUNICIPIOS-DEFUNCIONES.xls</t>
+          <t>POR-TIPO-1998-2023.xlsx</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-DEFUNCIONES.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-TIPO-1998-2023.xlsx</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Por Municipios</t>
+          <t>Por Variable</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas vitales</t>
+          <t>Encuesta de hogares</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>XLSX</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>POR-MUNICIPIOS-Matrimonios.xls</t>
+          <t>POR-VARIABLE-1998-2023.xlsx</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-Matrimonios.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-VARIABLE-1998-2023.xlsx</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Por Municipios</t>
+          <t>Divorcios</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>POR-MUNICIPIOS-nacimientos.xls</t>
+          <t>DIVORCIOS.xls</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-nacimientos.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/DIVORCIOS.xls</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Suicidios</t>
+          <t>Por Entidad</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>SUICIDIOS.xls</t>
+          <t>POR-ENTIDAD-Defunciones.xls</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/SUICIDIOS.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Defunciones.xls</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Por Entidad</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Otros recursos INE</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>Amazonas.xls</t>
+          <t>POR-ENTIDAD-Matrimonios.xls</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Amazonas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-Matrimonios.xls</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Por Entidad</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Otros recursos INE</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Estado-Amazonas-1.xls</t>
+          <t>POR-ENTIDAD-nacimientos.xls</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-ENTIDAD-nacimientos.xls</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
@@ -7228,12 +7228,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Por Municipios</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Otros recursos INE</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>Estado-Amazonas.xls</t>
+          <t>POR-MUNICIPIOS-DEFUNCIONES.xls</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-DEFUNCIONES.xls</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Por Municipios</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Otros recursos INE</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Estado_Amazonas-3.xls</t>
+          <t>POR-MUNICIPIOS-Matrimonios.xls</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Amazonas-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-Matrimonios.xls</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Por Municipios</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Otros recursos INE</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>Anzoategui.xls</t>
+          <t>POR-MUNICIPIOS-nacimientos.xls</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Anzoategui.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/POR-MUNICIPIOS-nacimientos.xls</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Suicidios</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Otros recursos INE</t>
+          <t>Estadísticas vitales</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>Estado-Anzoategui-1.xls</t>
+          <t>SUICIDIOS.xls</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/SUICIDIOS.xls</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Estado-Anzoategui.xls</t>
+          <t>Amazonas.xls</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Amazonas.xls</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>Estado_Anzoategui-3.xls</t>
+          <t>Estado-Amazonas-1.xls</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Anzoategui-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas-1.xls</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>Apure.xls</t>
+          <t>Estado-Amazonas.xls</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Apure.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Amazonas.xls</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Estado-Apure-1.xls</t>
+          <t>Estado_Amazonas-3.xls</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Amazonas-3.xls</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>Estado-Apure.xls</t>
+          <t>Anzoategui.xls</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Anzoategui.xls</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Estado_Apure-3.xls</t>
+          <t>Estado-Anzoategui-1.xls</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Apure-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui-1.xls</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Barinas.xls</t>
+          <t>Estado-Anzoategui.xls</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Barinas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Anzoategui.xls</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Estado-Barinas-1.xls</t>
+          <t>Estado_Anzoategui-3.xls</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Anzoategui-3.xls</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Estado-Barinas.xls</t>
+          <t>Apure.xls</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Apure.xls</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Estado_Barinas-3.xls</t>
+          <t>Estado-Apure-1.xls</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Barinas-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure-1.xls</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Bolivar.xls</t>
+          <t>Estado-Apure.xls</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Bolivar.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Apure.xls</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Estado-Bolivar-1.xls</t>
+          <t>Estado_Apure-3.xls</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Apure-3.xls</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Estado-Bolivar.xls</t>
+          <t>Barinas.xls</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Barinas.xls</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Estado_Bolivar-4.xls</t>
+          <t>Estado-Barinas-1.xls</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Bolivar-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas-1.xls</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Carabobo.xls</t>
+          <t>Estado-Barinas.xls</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Carabobo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Barinas.xls</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>Estado-Carabobo-1.xls</t>
+          <t>Estado_Barinas-3.xls</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Barinas-3.xls</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>Estado-Carabobo.xls</t>
+          <t>Bolivar.xls</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Bolivar.xls</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>Estado_Carabobo-4.xls</t>
+          <t>Estado-Bolivar-1.xls</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Carabobo-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar-1.xls</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>Cojedes.xls</t>
+          <t>Estado-Bolivar.xls</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Cojedes.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Bolivar.xls</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes-1.xls</t>
+          <t>Estado_Bolivar-4.xls</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Bolivar-4.xls</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes.xls</t>
+          <t>Carabobo.xls</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Carabobo.xls</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Estado_Cojedes-5.xls</t>
+          <t>Estado-Carabobo-1.xls</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Cojedes-5.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo-1.xls</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Delta-Amacuro.xls</t>
+          <t>Estado-Carabobo.xls</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Delta-Amacuro.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Carabobo.xls</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Estado-Delta-Amacuro-1.xls</t>
+          <t>Estado_Carabobo-4.xls</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Carabobo-4.xls</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>Estado-Delta-Amacuro.xls</t>
+          <t>Cojedes.xls</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Cojedes.xls</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Estado_DeltaAmacuro-4.xls</t>
+          <t>Estado-Cojedes-1.xls</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_DeltaAmacuro-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes-1.xls</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Dep. Federales</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>Dependencias-Federales-1.xls</t>
+          <t>Estado-Cojedes.xls</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Cojedes.xls</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Dep. Federales</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>Dependencias-Federales.xls</t>
+          <t>Estado_Cojedes-5.xls</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Cojedes-5.xls</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Dependencias_Federales-3.xls</t>
+          <t>Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias_Federales-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital-1.xls</t>
+          <t>Estado-Delta-Amacuro-1.xls</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro-1.xls</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital-2.xls</t>
+          <t>Estado-Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-2.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Delta-Amacuro.xls</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Distrito-Capital.xls</t>
+          <t>Estado_DeltaAmacuro-4.xls</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_DeltaAmacuro-4.xls</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Dep. Federales</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>Distrito_Capital-3.xls</t>
+          <t>Dependencias-Federales-1.xls</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito_Capital-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales-1.xls</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Dep. Federales</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -9367,12 +9367,12 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Estado-Falcon-1.xls</t>
+          <t>Dependencias-Federales.xls</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias-Federales.xls</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Estado-Falcon.xls</t>
+          <t>Dependencias_Federales-3.xls</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Dependencias_Federales-3.xls</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Estado_Falcon-4.xls</t>
+          <t>Distrito-Capital-1.xls</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Falcon-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-1.xls</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Falcon.xls</t>
+          <t>Distrito-Capital-2.xls</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Falcon.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital-2.xls</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico-1.xls</t>
+          <t>Distrito-Capital.xls</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito-Capital.xls</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico.xls</t>
+          <t>Distrito_Capital-3.xls</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Distrito_Capital-3.xls</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Estado_Guarico-4.xls</t>
+          <t>Estado-Falcon-1.xls</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Guarico-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon-1.xls</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Guarico.xls</t>
+          <t>Estado-Falcon.xls</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Guarico.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Falcon.xls</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira-1.xls</t>
+          <t>Estado_Falcon-4.xls</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Falcon-4.xls</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira.xls</t>
+          <t>Falcon.xls</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Falcon.xls</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Estado_Vargas-4.xls</t>
+          <t>Estado-Guarico-1.xls</t>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Vargas-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico-1.xls</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Vargas.xls</t>
+          <t>Estado-Guarico.xls</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Vargas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Guarico.xls</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Estado-Lara-1.xls</t>
+          <t>Estado_Guarico-4.xls</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Guarico-4.xls</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Estado-Lara.xls</t>
+          <t>Guarico.xls</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Guarico.xls</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Estado_Lara-3.xls</t>
+          <t>Estado-La-Guaira-1.xls</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Lara-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira-1.xls</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Lara.xls</t>
+          <t>Estado-La-Guaira.xls</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lara.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-La-Guaira.xls</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Estado-Miranda-1.xls</t>
+          <t>Estado_Vargas-4.xls</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Vargas-4.xls</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Estado-Miranda.xls</t>
+          <t>Vargas.xls</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Vargas.xls</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>Estado_Miranda-5.xls</t>
+          <t>Estado-Lara-1.xls</t>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Miranda-5.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara-1.xls</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Miranda.xls</t>
+          <t>Estado-Lara.xls</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Miranda.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Lara.xls</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>Estado-Monagas-1.xls</t>
+          <t>Estado_Lara-3.xls</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Lara-3.xls</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>Estado-Monagas.xls</t>
+          <t>Lara.xls</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Lara.xls</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>Estado_Monagas-4.xls</t>
+          <t>Estado-Miranda-1.xls</t>
         </is>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Monagas-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda-1.xls</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>Monagas.xls</t>
+          <t>Estado-Miranda.xls</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Monagas.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Miranda.xls</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Estado-Merida-1.xls</t>
+          <t>Estado_Miranda-5.xls</t>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Miranda-5.xls</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Estado-Merida.xls</t>
+          <t>Miranda.xls</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Miranda.xls</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Estado_Merida-4.xls</t>
+          <t>Estado-Monagas-1.xls</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Merida-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas-1.xls</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>Merida.xls</t>
+          <t>Estado-Monagas.xls</t>
         </is>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Merida.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Monagas.xls</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>Nacional-1.xls</t>
+          <t>Estado_Monagas-4.xls</t>
         </is>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Monagas-4.xls</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>Nacional.xls</t>
+          <t>Monagas.xls</t>
         </is>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Monagas.xls</t>
         </is>
       </c>
       <c r="K189" s="4" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>Estado-Nueva-Esparta-1.xls</t>
+          <t>Estado-Merida-1.xls</t>
         </is>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida-1.xls</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>Estado-Nueva-Esparta.xls</t>
+          <t>Estado-Merida.xls</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Merida.xls</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>Estado_NuevaEsparta-4.xls</t>
+          <t>Estado_Merida-4.xls</t>
         </is>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_NuevaEsparta-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Merida-4.xls</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>Nueva-Esparta.xls</t>
+          <t>Merida.xls</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nueva-Esparta.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Merida.xls</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>Estado-Portuguesa-1.xls</t>
+          <t>Nacional-1.xls</t>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-1.xls</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>Estado-Portuguesa.xls</t>
+          <t>Nacional.xls</t>
         </is>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional.xls</t>
         </is>
       </c>
       <c r="K195" s="4" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>Estado_Portuguesa-4.xls</t>
+          <t>Estado-Nueva-Esparta-1.xls</t>
         </is>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Portuguesa-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta-1.xls</t>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa.xls</t>
+          <t>Estado-Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Portuguesa.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="K197" s="4" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t>Estado-Sucre-1.xls</t>
+          <t>Estado_NuevaEsparta-4.xls</t>
         </is>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_NuevaEsparta-4.xls</t>
         </is>
       </c>
       <c r="K198" s="4" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t>Estado-Sucre.xls</t>
+          <t>Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nueva-Esparta.xls</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t>Estado_Sucre-6.xls</t>
+          <t>Estado-Portuguesa-1.xls</t>
         </is>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Sucre-6.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa-1.xls</t>
         </is>
       </c>
       <c r="K200" s="4" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t>Sucre.xls</t>
+          <t>Estado-Portuguesa.xls</t>
         </is>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Sucre.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Portuguesa.xls</t>
         </is>
       </c>
       <c r="K201" s="4" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Tachira</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
-          <t>Estado-Tachira.xls</t>
+          <t>Estado_Portuguesa-4.xls</t>
         </is>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Portuguesa-4.xls</t>
         </is>
       </c>
       <c r="K202" s="4" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo-1.xls</t>
+          <t>Portuguesa.xls</t>
         </is>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Portuguesa.xls</t>
         </is>
       </c>
       <c r="K203" s="4" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.xls</t>
+          <t>Estado-Sucre-1.xls</t>
         </is>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre-1.xls</t>
         </is>
       </c>
       <c r="K204" s="4" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="I205" s="4" t="inlineStr">
         <is>
-          <t>Estado_Trujillo-3.xls</t>
+          <t>Estado-Sucre.xls</t>
         </is>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Trujillo-3.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Sucre.xls</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
-          <t>Trujillo.xls</t>
+          <t>Estado_Sucre-6.xls</t>
         </is>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Trujillo.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Sucre-6.xls</t>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t>Estado-Tachira-1.xls</t>
+          <t>Sucre.xls</t>
         </is>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Sucre.xls</t>
         </is>
       </c>
       <c r="K207" s="4" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Tachira</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -12103,12 +12103,12 @@
       </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
-          <t>Estado_Tachira-8.xls</t>
+          <t>Estado-Tachira.xls</t>
         </is>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Tachira-8.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira.xls</t>
         </is>
       </c>
       <c r="K208" s="4" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t>Tachira.xls</t>
+          <t>Estado-Trujillo-1.xls</t>
         </is>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tachira.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo-1.xls</t>
         </is>
       </c>
       <c r="K209" s="4" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy-1.xls</t>
+          <t>Estado-Trujillo.xls</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Trujillo.xls</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy.xls</t>
+          <t>Estado_Trujillo-3.xls</t>
         </is>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Trujillo-3.xls</t>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t>Estado_Yaracuy-4.xls</t>
+          <t>Trujillo.xls</t>
         </is>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Yaracuy-4.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Trujillo.xls</t>
         </is>
       </c>
       <c r="K212" s="4" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy.xls</t>
+          <t>Estado-Tachira-1.xls</t>
         </is>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Yaracuy.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Tachira-1.xls</t>
         </is>
       </c>
       <c r="K213" s="4" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
-          <t>Estado-Zulia-1.xls</t>
+          <t>Estado_Tachira-8.xls</t>
         </is>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Tachira-8.xls</t>
         </is>
       </c>
       <c r="K214" s="4" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>Estado-Zulia.xls</t>
+          <t>Tachira.xls</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tachira.xls</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -12559,12 +12559,12 @@
       </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t>Estado_Zulia-6.xls</t>
+          <t>Estado-Yaracuy-1.xls</t>
         </is>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Zulia-6.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy-1.xls</t>
         </is>
       </c>
       <c r="K216" s="4" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>Zulia.xls</t>
+          <t>Estado-Yaracuy.xls</t>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Zulia.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Yaracuy.xls</t>
         </is>
       </c>
       <c r="K217" s="4" t="inlineStr">
@@ -12643,42 +12643,42 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Estructura Poblacional</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
-          <t>Estructura-completa.pdf</t>
+          <t>Estado_Yaracuy-4.xls</t>
         </is>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/09/Estructura-completa.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Yaracuy-4.xls</t>
         </is>
       </c>
       <c r="K218" s="4" t="inlineStr">
@@ -12700,22 +12700,22 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Población 1950-2050</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>Yaracuy.xls</t>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Yaracuy.xls</t>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr">
@@ -12757,12 +12757,12 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Edad Simple</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
-          <t>EDAD-SIMPLE.xls</t>
+          <t>Estado-Zulia-1.xls</t>
         </is>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia-1.xls</t>
         </is>
       </c>
       <c r="K220" s="4" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Esperanza de Vida</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t>ESPERANZA-DE-VIDA.xls</t>
+          <t>Estado-Zulia.xls</t>
         </is>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Zulia.xls</t>
         </is>
       </c>
       <c r="K221" s="4" t="inlineStr">
@@ -12871,12 +12871,12 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Proyección de población</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t>Nacional-36.xls</t>
+          <t>Estado_Zulia-6.xls</t>
         </is>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Zulia-6.xls</t>
         </is>
       </c>
       <c r="K222" s="4" t="inlineStr">
@@ -12928,42 +12928,42 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>7T FILVEN</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Otros recursos INE</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>Zulia.xls</t>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Zulia.xls</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Estructura Poblacional</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
@@ -13005,22 +13005,22 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2025.pdf</t>
+          <t>Estructura-completa.pdf</t>
         </is>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/09/Estructura-completa.pdf</t>
         </is>
       </c>
       <c r="K224" s="4" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Población 1950-2050</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -13067,17 +13067,17 @@
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ABRIL_2026.pdf</t>
+          <t>1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/1950-2050-REP.-BOL.-VENEZUELA-PROYECCION-POBLACION.pdf</t>
         </is>
       </c>
       <c r="K225" s="4" t="inlineStr">
@@ -13099,22 +13099,22 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Edad Simple</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -13124,17 +13124,17 @@
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t>Resumen_AGOSTO_2025.pdf</t>
+          <t>EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/EDAD-SIMPLE.xls</t>
         </is>
       </c>
       <c r="K226" s="4" t="inlineStr">
@@ -13156,42 +13156,42 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Esperanza de Vida</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-AMAZONAS.pdf</t>
+          <t>ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ESPERANZA-DE-VIDA.xls</t>
         </is>
       </c>
       <c r="K227" s="4" t="inlineStr">
@@ -13213,42 +13213,42 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Publicaciones</t>
+          <t>Proyección de población</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Dato tabular</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>XLS</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ANZOATEGUI.pdf</t>
+          <t>Nacional-36.xls</t>
         </is>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Nacional-36.xls</t>
         </is>
       </c>
       <c r="K228" s="4" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Apure</t>
+          <t>7T FILVEN</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -13295,17 +13295,17 @@
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-APURE.pdf</t>
+          <t>TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-CONOCE-EL-INE-INTEGRADO.pdf</t>
         </is>
       </c>
       <c r="K229" s="4" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Aviso Oficial Fe de Vida 2026</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -13352,17 +13352,17 @@
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ABRIL_2025.pdf</t>
         </is>
       </c>
       <c r="K230" s="4" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Barinas</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BARINAS.pdf</t>
+          <t>Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/05/Resumen_ABRIL_2026.pdf</t>
         </is>
       </c>
       <c r="K231" s="4" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-BOLIVAR.pdf</t>
+          <t>Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_AGOSTO_2025.pdf</t>
         </is>
       </c>
       <c r="K232" s="4" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>CATÁLOGO ACADÉMICO</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -13518,22 +13518,22 @@
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>CatalogoDic2025-modificado.pdf</t>
+          <t>Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto-9.pdf</t>
         </is>
       </c>
       <c r="K233" s="4" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -13575,22 +13575,22 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
-          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-AMAZONAS.pdf</t>
         </is>
       </c>
       <c r="K234" s="4" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -13642,12 +13642,12 @@
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-CARABOBO.pdf</t>
+          <t>ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ANZOATEGUI.pdf</t>
         </is>
       </c>
       <c r="K235" s="4" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Cojedes</t>
+          <t>Apure</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -13699,12 +13699,12 @@
       </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-COJEDES.pdf</t>
+          <t>ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-APURE.pdf</t>
         </is>
       </c>
       <c r="K236" s="4" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
+          <t>Aviso Oficial Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -13751,17 +13751,17 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr">
         <is>
-          <t>ART1DEFENSAINTEGRAL.pdf</t>
+          <t>AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/AVISO-OFICIAL-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K237" s="4" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Delta Amacuro</t>
+          <t>Barinas</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-DELTA-AMACURO.pdf</t>
+          <t>ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BARINAS.pdf</t>
         </is>
       </c>
       <c r="K238" s="4" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Dependencias Federales</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -13865,17 +13865,17 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-BOLIVAR.pdf</t>
         </is>
       </c>
       <c r="K239" s="4" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>CATÁLOGO ACADÉMICO</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -13917,22 +13917,22 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/12/CatalogoDic2025-modificado.pdf</t>
         </is>
       </c>
       <c r="K240" s="4" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Directrices</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -13979,17 +13979,17 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr">
         <is>
-          <t>DIRECTRICES.pdf</t>
+          <t>CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/CODIGO_DE_PRACTICAS_DE_LAS_ESTADISTICA.pdf</t>
         </is>
       </c>
       <c r="K241" s="4" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -14036,17 +14036,17 @@
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-CARABOBO.pdf</t>
         </is>
       </c>
       <c r="K242" s="4" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Distrito Capital</t>
+          <t>Cojedes</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -14098,12 +14098,12 @@
       </c>
       <c r="I243" s="4" t="inlineStr">
         <is>
-          <t>DISTRITO-CAPITAL.pdf</t>
+          <t>ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-COJEDES.pdf</t>
         </is>
       </c>
       <c r="K243" s="4" t="inlineStr">
@@ -14125,19 +14125,19 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
+          <t>Defensa Integral de la Nación e Innovación en la Fuerza Armada Nacional Bolivariana</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>Publicaciones</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
           <t>Documento</t>
         </is>
       </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>Publicaciones</t>
-        </is>
-      </c>
-      <c r="E244" s="4" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
@@ -14145,22 +14145,22 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-SEGEN.pdf</t>
+          <t>ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART1DEFENSAINTEGRAL.pdf</t>
         </is>
       </c>
       <c r="K244" s="4" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Documento Técnico EHM</t>
+          <t>Delta Amacuro</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -14202,22 +14202,22 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr">
         <is>
-          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-DELTA-AMACURO.pdf</t>
         </is>
       </c>
       <c r="K245" s="4" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
+          <t>Dependencias Federales</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -14259,22 +14259,22 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
-          <t>ART5ESTADODOCENTE.pdf</t>
+          <t>Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-de-las-Dependencias-Federales.pdf</t>
         </is>
       </c>
       <c r="K246" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="I247" s="4" t="inlineStr">
         <is>
-          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_DICIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K247" s="4" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Directrices</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -14373,22 +14373,22 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>Resumen_ENERO_2025.pdf</t>
+          <t>DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/DIRECTRICES.pdf</t>
         </is>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Estado Amazonas</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -14440,12 +14440,12 @@
       </c>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Dto.-Capital_20250629_154732_0000.pdf</t>
         </is>
       </c>
       <c r="K249" s="4" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Estado Anzoátegui</t>
+          <t>Distrito Capital</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -14492,17 +14492,17 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/DISTRITO-CAPITAL.pdf</t>
         </is>
       </c>
       <c r="K250" s="4" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Estado Apure</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="I251" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/DOCUMENTO-SEGEN.pdf</t>
         </is>
       </c>
       <c r="K251" s="4" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Estado Barinas</t>
+          <t>Documento Técnico EHM</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -14601,22 +14601,22 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/DOCUMENTO-TECNICO-EHM.pdf</t>
         </is>
       </c>
       <c r="K252" s="4" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Estado Bolívar</t>
+          <t>El Estado Docente y sus implicaciones jurídicas-filosóficas</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -14658,22 +14658,22 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART5ESTADODOCENTE.pdf</t>
         </is>
       </c>
       <c r="K253" s="4" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Estado Carabobo</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -14715,22 +14715,22 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/RESUMEN_NOTAS_ENERO_2026.pdf</t>
         </is>
       </c>
       <c r="K254" s="4" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Estado Cojedes</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -14772,22 +14772,22 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr">
         <is>
-          <t>Estado-Cojedes.pdf</t>
+          <t>Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_ENERO_2025.pdf</t>
         </is>
       </c>
       <c r="K255" s="4" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Estado Delta Amacuro</t>
+          <t>Estado Amazonas</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Amazonas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K256" s="4" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Estado Falcón</t>
+          <t>Estado Anzoátegui</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="I257" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Anzoategui-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K257" s="4" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Estado Guárico</t>
+          <t>Estado Apure</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
-          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Apure-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K258" s="4" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Estado La Guaira</t>
+          <t>Estado Barinas</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -15010,12 +15010,12 @@
       </c>
       <c r="I259" s="4" t="inlineStr">
         <is>
-          <t>Estado-La-Guaira.pdf</t>
+          <t>Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Barinas_20250623_102124_0000.pdf</t>
         </is>
       </c>
       <c r="K259" s="4" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Estado Lara</t>
+          <t>Estado Bolívar</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Bolivar-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K260" s="4" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Estado Miranda</t>
+          <t>Estado Carabobo</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -15124,12 +15124,12 @@
       </c>
       <c r="I261" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Carabobo-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K261" s="4" t="inlineStr">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Estado Monagas</t>
+          <t>Estado Cojedes</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -15181,12 +15181,12 @@
       </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Cojedes.pdf</t>
         </is>
       </c>
       <c r="K262" s="4" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Estado Mérida</t>
+          <t>Estado Delta Amacuro</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -15238,12 +15238,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Delta-Amacuro-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K263" s="4" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Estado Nueva Esparta</t>
+          <t>Estado Falcón</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Falcon-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K264" s="4" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Estado Portuguesa</t>
+          <t>Estado Guárico</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="I265" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
+          <t>Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Guarico_20250620_153508_0000.pdf</t>
         </is>
       </c>
       <c r="K265" s="4" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Estado Sucre</t>
+          <t>Estado La Guaira</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-La-Guaira.pdf</t>
         </is>
       </c>
       <c r="K266" s="4" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Estado Trujillo</t>
+          <t>Estado Lara</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="I267" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Lara-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K267" s="4" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Estado Táchira</t>
+          <t>Estado Miranda</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Estado-Tachira.pdf</t>
+          <t>Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Miranda-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K268" s="4" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Estado Yaracuy</t>
+          <t>Estado Monagas</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="I269" s="4" t="inlineStr">
         <is>
-          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Monagas-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K269" s="4" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Estado Zulia</t>
+          <t>Estado Mérida</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -15637,12 +15637,12 @@
       </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
-          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Merida-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K270" s="4" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Estadísticas Basadas en Registros</t>
+          <t>Estado Nueva Esparta</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -15684,22 +15684,22 @@
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I271" s="4" t="inlineStr">
         <is>
-          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nueva-Esparta-_20250628_141737_0000.pdf</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
+          <t>Estado Portuguesa</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -15741,22 +15741,22 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr">
         <is>
-          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
         </is>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Portuguesa-_20250629_131617_0000.pdf</t>
         </is>
       </c>
       <c r="K272" s="4" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Falcón</t>
+          <t>Estado Sucre</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -15803,17 +15803,17 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-FALCON.pdf</t>
+          <t>Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Sucre-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K273" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Estado Trujillo</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
-          <t>Resumen_FEBRERO_2025.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K274" s="4" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Estado Táchira</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -15912,22 +15912,22 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr">
         <is>
-          <t>febrero.pdf</t>
+          <t>Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Estado-Tachira.pdf</t>
         </is>
       </c>
       <c r="K275" s="4" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Flyer</t>
+          <t>Estado Yaracuy</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -15969,22 +15969,22 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I276" s="4" t="inlineStr">
         <is>
-          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Yaracuy_20250619_231832_0000.pdf</t>
         </is>
       </c>
       <c r="K276" s="4" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Folleto en PDF</t>
+          <t>Estado Zulia</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -16026,22 +16026,22 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I277" s="4" t="inlineStr">
         <is>
-          <t>TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-del-Estado-Zulia-INE-2025.pdf</t>
         </is>
       </c>
       <c r="K277" s="4" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Formato de Fe de Vida 2026</t>
+          <t>Estadísticas Basadas en Registros</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -16083,22 +16083,22 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I278" s="4" t="inlineStr">
         <is>
-          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/ESTADISTICAS-BASADAS-EN-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K278" s="4" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Gestion y Mantenimiento</t>
+          <t>Estudio de la narrativa audiovisual como espacio de autodescubrimiento</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -16140,22 +16140,22 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr">
         <is>
-          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART6CINEYSUBJETIVIDAD.pdf</t>
         </is>
       </c>
       <c r="K279" s="4" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Grandes Misiones Habitacionales</t>
+          <t>Falcón</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -16197,22 +16197,22 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-FALCON.pdf</t>
         </is>
       </c>
       <c r="K280" s="4" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Guárico</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -16254,22 +16254,22 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-GUARICO.pdf</t>
+          <t>Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_FEBRERO_2025.pdf</t>
         </is>
       </c>
       <c r="K281" s="4" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>INE – FILVEN</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -16311,22 +16311,22 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>febrero.pdf</t>
         </is>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/febrero.pdf</t>
         </is>
       </c>
       <c r="K282" s="4" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Flyer</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -16368,22 +16368,22 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>25-anos-Encuesta-Industrial-.pdf</t>
+          <t>Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/Flyer-Avance-Nuevo-Portal-Web-INE-11102024-Final.pdf</t>
         </is>
       </c>
       <c r="K283" s="4" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Folleto en PDF</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -16425,22 +16425,22 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JULIO_2025.pdf</t>
+          <t>TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/09/TRANSICION-DEMOGRAFICA.pdf</t>
         </is>
       </c>
       <c r="K284" s="4" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Formato de Fe de Vida 2026</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -16487,17 +16487,17 @@
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="I285" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Julio-31.pdf</t>
+          <t>FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/01/FORMATO-DE-FE-DE-VIDA-2026.pdf</t>
         </is>
       </c>
       <c r="K285" s="4" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Gestion y Mantenimiento</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -16539,22 +16539,22 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I286" s="4" t="inlineStr">
         <is>
-          <t>Resumen_JUNIO_2025.pdf</t>
+          <t>GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/GESTION-Y-MANTENIMIENTO.pdf</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Grandes Misiones Habitacionales</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -16601,17 +16601,17 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>Noticias-12-06-al-19-06.pdf</t>
+          <t>Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Grandes_Misiones_habitacionales_de_Venezuela_CHN.pdf</t>
         </is>
       </c>
       <c r="K287" s="4" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>La Guaira</t>
+          <t>Guárico</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -16663,12 +16663,12 @@
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LA-GUAIRA.pdf</t>
+          <t>ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-GUARICO.pdf</t>
         </is>
       </c>
       <c r="K288" s="4" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Lara</t>
+          <t>INE – FILVEN</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -16715,17 +16715,17 @@
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-LARA.pdf</t>
+          <t>TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-LA-JUVENTUD-7T-FILVEN-JULIO-2025.pdf</t>
         </is>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Las escala subregional y local en la planificación</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -16772,17 +16772,17 @@
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/25-anos-Encuesta-Industrial-.pdf</t>
         </is>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -16824,22 +16824,22 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>MANUAL.pdf</t>
+          <t>Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JULIO_2025.pdf</t>
         </is>
       </c>
       <c r="K291" s="4" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Mapa Pobreza XII Censo</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -16886,17 +16886,17 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Julio-31.pdf</t>
         </is>
       </c>
       <c r="K292" s="4" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -16948,12 +16948,12 @@
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2025.pdf</t>
+          <t>Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_JUNIO_2025.pdf</t>
         </is>
       </c>
       <c r="K293" s="4" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -17000,17 +17000,17 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MARZO_2026.pdf</t>
+          <t>Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Noticias-12-06-al-19-06.pdf</t>
         </is>
       </c>
       <c r="K294" s="4" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>La Guaira</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -17052,22 +17052,22 @@
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2025.pdf</t>
+          <t>ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LA-GUAIRA.pdf</t>
         </is>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -17109,22 +17109,22 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>Resumen_MAYO_2026-1.pdf</t>
+          <t>ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-LARA.pdf</t>
         </is>
       </c>
       <c r="K296" s="4" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Las escala subregional y local en la planificación</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -17166,22 +17166,22 @@
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I297" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MIRANDA.pdf</t>
+          <t>E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/E3LASESCALASSUBREGIONAL.pdf</t>
         </is>
       </c>
       <c r="K297" s="4" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -17223,22 +17223,22 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MONAGAS.pdf</t>
+          <t>MANUAL.pdf</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/MANUAL.pdf</t>
         </is>
       </c>
       <c r="K298" s="4" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Mérida</t>
+          <t>Mapa Pobreza XII Censo</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -17280,22 +17280,22 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-MERIDA.pdf</t>
+          <t>Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Mapa-de-la-Pobreza-Basado-en-los-resultados-del-XII-CENSO-GENERAL.pdf</t>
         </is>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -17337,22 +17337,22 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MARZO_2025.pdf</t>
         </is>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto5.pdf</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -17399,17 +17399,17 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>Noticias-Agosto5.pdf</t>
+          <t>Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/08/Noticias-Agosto5.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/Resumen_MARZO_2026.pdf</t>
         </is>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17461,12 +17461,12 @@
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>Notas_Nov_2025.pdf</t>
+          <t>Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_MAYO_2025.pdf</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -17508,22 +17508,22 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/06/Resumen_MAYO_2026-1.pdf</t>
         </is>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -17565,22 +17565,22 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>Resumen_OCTUBRE_2025.pdf</t>
+          <t>ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MIRANDA.pdf</t>
         </is>
       </c>
       <c r="K304" s="4" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>PLAN DE LA PATRIA 7T</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -17627,17 +17627,17 @@
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>7TLeyPlanPatriaF.pdf</t>
+          <t>ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MONAGAS.pdf</t>
         </is>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -17679,22 +17679,22 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>Plan-Patria-2019-2025-1.pdf</t>
+          <t>ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-MERIDA.pdf</t>
         </is>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -17736,22 +17736,22 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>Plan_Estrategico_2014-2019.pdf</t>
+          <t>Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Folleto-Nacional-Venezuela-y-las-7T.pdf</t>
         </is>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Portal Web</t>
+          <t>Noticias-Septiembre-1.pdf</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -17793,22 +17793,22 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>Noticias-Septiembre-1.pdf</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/09/Noticias-Septiembre-1.pdf</t>
         </is>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Portuguesa</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -17850,22 +17850,22 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-PORTUGUESA.pdf</t>
+          <t>Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Notas_Nov_2025.pdf</t>
         </is>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Programación</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -17912,17 +17912,17 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-NUEVA-ESPARTA.pdf</t>
         </is>
       </c>
       <c r="K310" s="4" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Registros Administrativos Economicos</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -17964,22 +17964,22 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I311" s="4" t="inlineStr">
         <is>
-          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_OCTUBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K311" s="4" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Revista ÁGORA</t>
+          <t>PLAN DE LA PATRIA 7T</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18021,22 +18021,22 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>REVISTA-AGORA-1.pdf</t>
+          <t>7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/06/7TLeyPlanPatriaF.pdf</t>
         </is>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -18078,22 +18078,22 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr">
         <is>
-          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan-Patria-2019-2025-1.pdf</t>
         </is>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Sistema de Registros</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -18140,17 +18140,17 @@
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA-DE-REGISTROS.pdf</t>
+          <t>Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Plan_Estrategico_2014-2019.pdf</t>
         </is>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>Portal Web</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -18192,22 +18192,22 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I315" s="4" t="inlineStr">
         <is>
-          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/TRIPTICO-INTEGRADO-PORTAL-WEB.pdf</t>
         </is>
       </c>
       <c r="K315" s="4" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Portuguesa</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -18259,12 +18259,12 @@
       </c>
       <c r="I316" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-SUCRE.pdf</t>
+          <t>ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-PORTUGUESA.pdf</t>
         </is>
       </c>
       <c r="K316" s="4" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Síntesis</t>
+          <t>Programación</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="I317" s="4" t="inlineStr">
         <is>
-          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/PROGRAMACION-FILVEN-09-07-25.pdf</t>
         </is>
       </c>
       <c r="K317" s="4" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
+          <t>Registros Administrativos Economicos</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -18363,22 +18363,22 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I318" s="4" t="inlineStr">
         <is>
-          <t>Tipologia.pdf</t>
+          <t>REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/REGISTROS-ADMINISTRATIVOS-ECONOMICOS.pdf</t>
         </is>
       </c>
       <c r="K318" s="4" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Trujillo</t>
+          <t>Revista ÁGORA</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -18425,17 +18425,17 @@
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>Estado-Trujillo.pdf</t>
+          <t>REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/REVISTA-AGORA-1.pdf</t>
         </is>
       </c>
       <c r="K319" s="4" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Táchira</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -18477,22 +18477,22 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="I320" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-TACHIRA.pdf</t>
+          <t>Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/02/Resumen_SEPTIEMBRE_2025.pdf</t>
         </is>
       </c>
       <c r="K320" s="4" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
+          <t>Sistema de Registros</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -18534,22 +18534,22 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="I321" s="4" t="inlineStr">
         <is>
-          <t>ART2GOBDELFUTURO.pdf</t>
+          <t>SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/10/SISTEMA-DE-REGISTROS.pdf</t>
         </is>
       </c>
       <c r="K321" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Yaracuy</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -18591,22 +18591,22 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I322" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-YARACUY.pdf</t>
+          <t>Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Sistema-Estadistico-y-Geografico-Nacional.pdf</t>
         </is>
       </c>
       <c r="K322" s="4" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Zulia</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -18658,12 +18658,12 @@
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ZULIA.pdf</t>
+          <t>ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-SUCRE.pdf</t>
         </is>
       </c>
       <c r="K323" s="4" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
+          <t>Síntesis</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -18705,22 +18705,22 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="I324" s="4" t="inlineStr">
         <is>
-          <t>vision-metodologica.pdf</t>
+          <t>Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2024/08/Resumen_de_estadisticas_1999-2023.pdf</t>
         </is>
       </c>
       <c r="K324" s="4" t="inlineStr">
@@ -18742,12 +18742,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Tipología Sociales. Síntesis e impulso de dinámicas sociales.</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -18762,22 +18762,22 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>ESTADO-ARAGUA.pdf</t>
+          <t>Tipologia.pdf</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Tipologia.pdf</t>
         </is>
       </c>
       <c r="K325" s="4" t="inlineStr">
@@ -18799,12 +18799,12 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Censo de zonas afectadas del estado Vargas</t>
+          <t>Trujillo</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr">
@@ -18829,12 +18829,12 @@
       </c>
       <c r="I326" s="4" t="inlineStr">
         <is>
-          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/Estado-Trujillo.pdf</t>
         </is>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -18856,12 +18856,12 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Hogares 1967-1997</t>
+          <t>Táchira</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -18876,22 +18876,22 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-TACHIRA.pdf</t>
         </is>
       </c>
       <c r="K327" s="4" t="inlineStr">
@@ -18913,12 +18913,12 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Estado Aragua</t>
+          <t>Uso intensivo de datos e inteligencia artificial para las políticas públicas</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr">
@@ -18933,22 +18933,22 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="I328" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua_compressed.pdf</t>
+          <t>ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/ART2GOBDELFUTURO.pdf</t>
         </is>
       </c>
       <c r="K328" s="4" t="inlineStr">
@@ -18970,12 +18970,12 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Yaracuy</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -18990,22 +18990,22 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>VIVIENDA.pdf</t>
+          <t>ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-YARACUY.pdf</t>
         </is>
       </c>
       <c r="K329" s="4" t="inlineStr">
@@ -19027,42 +19027,42 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>Zulia</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>Aragua.xls</t>
+          <t>ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ZULIA.pdf</t>
         </is>
       </c>
       <c r="K330" s="4" t="inlineStr">
@@ -19084,22 +19084,22 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Aragua</t>
+          <t>visión metodológica para la clasificación de paisajes ecológicos</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y servicios</t>
+          <t>Publicaciones</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G331" s="4" t="inlineStr">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua-1.xls</t>
+          <t>vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/vision-metodologica.pdf</t>
         </is>
       </c>
       <c r="K331" s="4" t="inlineStr">
@@ -19151,32 +19151,32 @@
       </c>
       <c r="E332" s="4" t="inlineStr">
         <is>
-          <t>Dato tabular</t>
+          <t>Documento</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>XLS</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="I332" s="4" t="inlineStr">
         <is>
-          <t>Estado-Aragua.xls</t>
+          <t>ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
-          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/11/ESTADO-ARAGUA.pdf</t>
         </is>
       </c>
       <c r="K332" s="4" t="inlineStr">
@@ -19198,45 +19198,444 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
+          <t>Censo de zonas afectadas del estado Vargas</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H333" s="4" t="inlineStr">
+        <is>
+          <t>julio</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/CENSO-DE-ESTRUCTURAS-VIVIENDAS-Y-PERSONAS-EN-LAS-ZONAS-AFECTADAS-DEL-ESTADO-VARGAS.pdf</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>Encuesta Hogares 1967-1997</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E334" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H334" s="4" t="inlineStr">
+        <is>
+          <t>marzo</t>
+        </is>
+      </c>
+      <c r="I334" s="4" t="inlineStr">
+        <is>
+          <t>ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+        </is>
+      </c>
+      <c r="J334" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/03/ENCUESTA-DE-HOGARES-POR-MUESTREO-1967-1997_compressed.pdf</t>
+        </is>
+      </c>
+      <c r="K334" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>Estado Aragua</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E335" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G335" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H335" s="4" t="inlineStr">
+        <is>
+          <t>julio</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua_compressed.pdf</t>
+        </is>
+      </c>
+      <c r="J335" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2025/07/Estado-Aragua_compressed.pdf</t>
+        </is>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H336" s="4" t="inlineStr">
+        <is>
+          <t>julio</t>
+        </is>
+      </c>
+      <c r="I336" s="4" t="inlineStr">
+        <is>
+          <t>VIVIENDA.pdf</t>
+        </is>
+      </c>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/07/VIVIENDA.pdf</t>
+        </is>
+      </c>
+      <c r="K336" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
           <t>Aragua</t>
         </is>
       </c>
-      <c r="D333" s="4" t="inlineStr">
+      <c r="D337" s="4" t="inlineStr">
         <is>
           <t>Vivienda y servicios</t>
         </is>
       </c>
-      <c r="E333" s="4" t="inlineStr">
-        <is>
-          <t>Dato tabular</t>
-        </is>
-      </c>
-      <c r="F333" s="4" t="inlineStr">
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
         <is>
           <t>XLS</t>
         </is>
       </c>
-      <c r="G333" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H333" s="4" t="inlineStr">
-        <is>
-          <t>abril</t>
-        </is>
-      </c>
-      <c r="I333" s="4" t="inlineStr">
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G338" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H338" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I338" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua-1.xls</t>
+        </is>
+      </c>
+      <c r="K338" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E339" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H339" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I339" s="4" t="inlineStr">
+        <is>
+          <t>Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="J339" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado-Aragua.xls</t>
+        </is>
+      </c>
+      <c r="K339" s="4" t="inlineStr">
+        <is>
+          <t>https://ine.gob.ve/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>INE Venezuela - Instituto Nacional de Estadística</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>Aragua</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr">
+        <is>
+          <t>Vivienda y servicios</t>
+        </is>
+      </c>
+      <c r="E340" s="4" t="inlineStr">
+        <is>
+          <t>Dato tabular</t>
+        </is>
+      </c>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>XLS</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H340" s="4" t="inlineStr">
+        <is>
+          <t>abril</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr">
         <is>
           <t>Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="J333" s="4" t="inlineStr">
+      <c r="J340" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/wp-content/uploads/2026/04/Estado_Aragua-3.xls</t>
         </is>
       </c>
-      <c r="K333" s="4" t="inlineStr">
+      <c r="K340" s="4" t="inlineStr">
         <is>
           <t>https://ine.gob.ve/</t>
         </is>
@@ -19322,7 +19721,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -19369,7 +19768,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14">
@@ -19389,7 +19788,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
